--- a/product_selector_out/STM32G4 series - diff.xlsx
+++ b/product_selector_out/STM32G4 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,21 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5121</v>
+        <v>5146</v>
       </c>
     </row>
     <row r="18">
@@ -2921,22 +2903,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2948,67 +2926,59 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G431VB</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32G431VB</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -3020,18 +2990,18 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32G431VB</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -3043,18 +3013,18 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -3066,18 +3036,18 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -3089,88 +3059,76 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3193,7 +3151,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3216,7 +3174,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3239,7 +3197,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3262,99 +3220,87 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -3366,18 +3312,18 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -3389,88 +3335,76 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3493,7 +3427,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3516,99 +3450,87 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -3620,18 +3542,18 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -3643,18 +3565,18 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -3666,18 +3588,18 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -3689,18 +3611,18 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -3712,18 +3634,18 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -3735,88 +3657,76 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3839,7 +3749,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3862,99 +3772,87 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -3966,18 +3864,18 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -3989,88 +3887,76 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E161" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4093,7 +3979,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4116,99 +4002,87 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E166" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -4220,18 +4094,18 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -4243,88 +4117,76 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E171" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4347,7 +4209,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4370,7 +4232,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4393,7 +4255,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4416,99 +4278,87 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -4520,18 +4370,18 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -4543,18 +4393,18 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
@@ -4566,18 +4416,18 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -4589,1921 +4439,28 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>STM32G491KE</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>STM32G491KE</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>STM32G491KE</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>STM32G491KE</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>STM32G491KC</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>STM32G491KC</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>STM32G491KC</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>STM32G491KC</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>STM32G491KC</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>STM32G441CB</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>STM32G441CB</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>STM32G491VC</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>STM32G491VC</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E197" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>STM32G491VC</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E198" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>STM32G491VC</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>STM32G491VC</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>STM32G431K6</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>STM32G431K6</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>STM32G431K6</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>STM32G431K6</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>STM32G431K6</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>STM32G441MB</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>STM32G441MB</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>STM32G431R8</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>STM32G431R8</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E209" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>STM32G431R8</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E210" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>STM32G431R8</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>STM32G431R8</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>STM32G4A1VE</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>STM32G4A1VE</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>STM32G431R6</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E215" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>STM32G431R6</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E216" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>STM32G431R6</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E217" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>STM32G431R6</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>STM32G431R6</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>STM32G431M8</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>STM32G431M8</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E221" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>STM32G431M8</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E222" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>STM32G431M8</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>STM32G431M8</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>STM32G431C8</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E225" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>STM32G431C8</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E226" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>STM32G431C8</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E227" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>STM32G431C8</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>STM32G431C8</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>STM32G431MB</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>STM32G431MB</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E231" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>STM32G431MB</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E232" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>STM32G431MB</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>STM32G431MB</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>STM32G431C6</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>STM32G431C6</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E236" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>STM32G431C6</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E237" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>STM32G431C6</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>STM32G431C6</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>STM32G431KB</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E240" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>STM32G431KB</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E241" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>STM32G431KB</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E242" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>STM32G431KB</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>STM32G431KB</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E246" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E247" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E250" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E251" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E252" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E253" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E254" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E255" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E256" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>11 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E257" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E259"/>
+  <autoFilter ref="A18:E184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32G4 series - diff.xlsx
+++ b/product_selector_out/STM32G4 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -541,7 +547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5146</v>
+        <v>5138</v>
       </c>
     </row>
     <row r="18">
@@ -1753,18 +1759,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1776,13 +1786,13 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -1794,18 +1804,18 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G474QB</t>
+          <t>STM32G474CB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -1822,13 +1832,13 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -1840,18 +1850,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G474VE</t>
+          <t>STM32G474QB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -1868,13 +1878,13 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -1886,18 +1896,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G474VC</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -1914,13 +1924,13 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -1932,18 +1942,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G474VB</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -1960,13 +1970,13 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -1978,18 +1988,18 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G484QE</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2006,13 +2016,13 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2024,18 +2034,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G474ME</t>
+          <t>STM32G484QE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2052,13 +2062,13 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -2070,18 +2080,18 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G484VE</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -2098,13 +2108,13 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -2116,18 +2126,18 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G474RE</t>
+          <t>STM32G484VE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2144,13 +2154,13 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -2162,18 +2172,18 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G474PC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2190,13 +2200,13 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2208,18 +2218,18 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G484ME</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2236,13 +2246,13 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -2254,18 +2264,18 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G474RC</t>
+          <t>STM32G484ME</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -2282,13 +2292,13 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -2300,18 +2310,18 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G474MC</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -2328,13 +2338,13 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -2346,18 +2356,18 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G474MB</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2374,13 +2384,13 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -2392,18 +2402,18 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G484RE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -2420,13 +2430,13 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -2438,18 +2448,18 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G474RB</t>
+          <t>STM32G484RE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -2466,13 +2476,13 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -2484,18 +2494,18 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G484CE</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -2512,13 +2522,13 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -2530,18 +2540,18 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G484CE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -2558,25 +2568,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2599,7 +2613,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2622,7 +2636,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G474QE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2645,7 +2659,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G474QE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2668,41 +2682,45 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -2714,18 +2732,18 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -2737,18 +2755,18 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G474QC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -2760,18 +2778,18 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474QC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -2783,18 +2801,18 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474PE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -2806,18 +2824,18 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474PE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -2829,18 +2847,18 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474PB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -2852,18 +2870,18 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G441KB</t>
+          <t>STM32G474PB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -2875,18 +2893,18 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G441KB</t>
+          <t>STM32G484PE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -2898,18 +2916,18 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G431VB</t>
+          <t>STM32G484PE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -2921,18 +2939,18 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G431VB</t>
+          <t>STM32G441KB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -2944,18 +2962,18 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G441KB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -2967,18 +2985,18 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431VB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -2990,18 +3008,18 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G431VB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -3013,18 +3031,18 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -3036,18 +3054,18 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -3059,18 +3077,18 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -3082,18 +3100,18 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -3105,18 +3123,18 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -3128,18 +3146,18 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -3151,18 +3169,18 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -3174,18 +3192,18 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -3197,18 +3215,18 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -3220,18 +3238,18 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -3243,18 +3261,18 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -3266,18 +3284,18 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -3289,18 +3307,18 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -3312,18 +3330,18 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -3335,18 +3353,18 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -3358,18 +3376,18 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -3381,18 +3399,18 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -3404,18 +3422,18 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -3427,18 +3445,18 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -3450,18 +3468,18 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -3473,18 +3491,18 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -3496,18 +3514,18 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -3519,18 +3537,18 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -3542,18 +3560,18 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -3565,18 +3583,18 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -3588,18 +3606,18 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -3611,18 +3629,18 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -3634,18 +3652,18 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -3657,18 +3675,18 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -3680,18 +3698,18 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -3703,18 +3721,18 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -3726,18 +3744,18 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -3749,30 +3767,34 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3795,7 +3817,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3818,41 +3840,45 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -3864,18 +3890,18 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -3887,18 +3913,18 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -3910,18 +3936,18 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -3933,18 +3959,18 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -3956,18 +3982,18 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -3979,30 +4005,34 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4025,7 +4055,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4048,7 +4078,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4071,7 +4101,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4094,7 +4124,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4117,7 +4147,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4140,7 +4170,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4163,7 +4193,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4186,7 +4216,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4209,7 +4239,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4232,7 +4262,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4255,7 +4285,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4278,7 +4308,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4301,7 +4331,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4324,7 +4354,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4347,7 +4377,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4370,7 +4400,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4393,7 +4423,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4416,41 +4446,45 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -4459,8 +4493,196 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E184"/>
+  <autoFilter ref="A18:E192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32G4 series - diff.xlsx
+++ b/product_selector_out/STM32G4 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$235</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5312</v>
+        <v>5395</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5138</v>
+        <v>5178</v>
       </c>
     </row>
     <row r="18">
@@ -1827,18 +1827,18 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G474QB</t>
+          <t>STM32G474CB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -1855,13 +1855,13 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -1873,18 +1873,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G474VE</t>
+          <t>STM32G474QB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -1896,18 +1896,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G474VE</t>
+          <t>STM32G474QB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G474VC</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G474VC</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1965,18 +1965,18 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G474VB</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -1988,18 +1988,18 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G474VB</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2011,18 +2011,18 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G484QE</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2034,18 +2034,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G484QE</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2057,7 +2057,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G474ME</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G474ME</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2103,18 +2103,18 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G484VE</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -2126,18 +2126,18 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G484VE</t>
+          <t>STM32G484QE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -2149,18 +2149,18 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G474RE</t>
+          <t>STM32G484QE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -2172,18 +2172,18 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G474RE</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2195,18 +2195,18 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G474PC</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2218,18 +2218,18 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G474PC</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -2241,7 +2241,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G484ME</t>
+          <t>STM32G484VE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2264,7 +2264,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G484ME</t>
+          <t>STM32G484VE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G474RC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G474RC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2333,18 +2333,18 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G474MC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -2356,18 +2356,18 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G474MC</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2379,18 +2379,18 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G474MB</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -2402,18 +2402,18 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G474MB</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G484RE</t>
+          <t>STM32G484ME</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2448,7 +2448,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G484RE</t>
+          <t>STM32G484ME</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G474RB</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2494,7 +2494,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G474RB</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2517,18 +2517,18 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G484CE</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -2540,18 +2540,18 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G484CE</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -2563,45 +2563,41 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -2613,18 +2609,18 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -2636,18 +2632,18 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -2659,18 +2655,18 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -2682,45 +2678,41 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G484RE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G484RE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -2732,18 +2724,18 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -2755,18 +2747,18 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -2778,18 +2770,18 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -2801,7 +2793,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G484CE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2824,7 +2816,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G484CE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2847,41 +2839,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -2893,18 +2889,18 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -2916,18 +2912,18 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -2939,7 +2935,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G441KB</t>
+          <t>STM32G474QE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2962,7 +2958,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G441KB</t>
+          <t>STM32G474QE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2985,18 +2981,18 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32G431VB</t>
+          <t>STM32G474QE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -3008,30 +3004,34 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32G431VB</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3054,7 +3054,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3077,18 +3077,18 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -3100,18 +3100,18 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G474QC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -3123,18 +3123,18 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G474QC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -3146,18 +3146,18 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G474QC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -3169,7 +3169,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G474PE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3192,7 +3192,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G474PE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3215,18 +3215,18 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G474PE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -3238,18 +3238,18 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G474PB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -3261,18 +3261,18 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G474PB</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -3284,18 +3284,18 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G474PB</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G484PE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3330,7 +3330,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G484PE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G441KB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G441KB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3399,7 +3399,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431VB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431VB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3445,18 +3445,18 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G431VB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -3468,18 +3468,18 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -3491,18 +3491,18 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -3514,18 +3514,18 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -3537,18 +3537,18 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -3560,18 +3560,18 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -3583,7 +3583,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3675,18 +3675,18 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -3698,18 +3698,18 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -3721,18 +3721,18 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -3744,18 +3744,18 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -3767,45 +3767,41 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -3817,18 +3813,18 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -3840,45 +3836,41 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -3890,18 +3882,18 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -3913,18 +3905,18 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -3936,18 +3928,18 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -3959,18 +3951,18 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -3982,18 +3974,18 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -4005,45 +3997,41 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -4055,18 +4043,18 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -4078,7 +4066,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4101,7 +4089,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4124,18 +4112,18 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -4147,18 +4135,18 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -4170,18 +4158,18 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -4193,18 +4181,18 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -4216,7 +4204,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4239,7 +4227,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4262,18 +4250,18 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
@@ -4285,18 +4273,18 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -4308,18 +4296,18 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
@@ -4331,18 +4319,18 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -4354,18 +4342,18 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
@@ -4377,18 +4365,18 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -4400,7 +4388,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4423,7 +4411,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4446,7 +4434,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4473,7 +4461,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4496,7 +4484,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4519,68 +4507,68 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -4592,18 +4580,18 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -4615,18 +4603,18 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
@@ -4638,7 +4626,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4661,7 +4649,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4681,8 +4669,1009 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>STM32G491VC</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>STM32G491VC</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>STM32G491VC</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>STM32G431K6</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>STM32G431K6</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>STM32G431K6</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>STM32G431K6</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>STM32G441MB</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>STM32G441MB</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>STM32G431R8</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>STM32G431R8</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>STM32G431R8</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>STM32G4A1VE</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>STM32G4A1VE</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>STM32G431R6</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>STM32G431R6</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>STM32G431R6</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>STM32G431M8</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>STM32G431M8</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>STM32G431M8</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>STM32G431C8</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>STM32G431C8</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>STM32G431C8</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>STM32G431MB</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>STM32G431MB</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>STM32G431MB</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>STM32G431C6</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>STM32G431C6</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>STM32G431C6</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E192"/>
+  <autoFilter ref="A18:E235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>